--- a/OrderbookAutomation/output/Derived_Data.xlsx
+++ b/OrderbookAutomation/output/Derived_Data.xlsx
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.52</v>
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>

--- a/OrderbookAutomation/output/Derived_Data.xlsx
+++ b/OrderbookAutomation/output/Derived_Data.xlsx
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.82</v>
+        <v>2.06</v>
       </c>
     </row>
   </sheetData>
